--- a/data/power-electronics/sic-diodes.xlsx
+++ b/data/power-electronics/sic-diodes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\power-electronics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67089CCB-B999-4BDF-BD75-6CF2885C5A25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F741B0AD-2AF0-4ADA-928A-5C34375E8530}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
   <si>
     <t>Brand</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Tj (°C)</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -503,21 +506,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" customWidth="1"/>
-    <col min="4" max="4" width="49" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="51.140625" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
+    <col min="11" max="11" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -525,1243 +528,1360 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3">
+        <v>401</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3">
         <v>650</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>4</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>1.27</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="3">
         <v>32</v>
       </c>
-      <c r="I2" s="3">
+      <c r="J2" s="3">
         <v>11.5</v>
       </c>
-      <c r="J2" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3">
+        <v>402</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
         <v>650</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>4</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>1.27</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>32</v>
       </c>
-      <c r="I3" s="3">
+      <c r="J3" s="3">
         <v>11.5</v>
       </c>
-      <c r="J3" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3">
+        <v>403</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3">
         <v>650</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>6</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>1.27</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>52</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>17</v>
       </c>
-      <c r="J4" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3">
+        <v>404</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
         <v>650</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>6</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1.27</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>52</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>17</v>
       </c>
-      <c r="J5" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3">
+        <v>405</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3">
         <v>650</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>6</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1.27</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>52</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>17</v>
       </c>
-      <c r="J6" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3">
+        <v>406</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
         <v>650</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>8</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>1.27</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>72</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>21</v>
       </c>
-      <c r="J7" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3">
+        <v>407</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>650</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1.27</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>72</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21</v>
       </c>
-      <c r="J8" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3">
+        <v>408</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
         <v>650</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1.27</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>72</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3">
+        <v>409</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
         <v>650</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1.27</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25</v>
       </c>
-      <c r="J10" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3">
+        <v>410</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="E11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3">
         <v>650</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>10</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>1.27</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>80</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>25</v>
       </c>
-      <c r="J11" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3">
+        <v>411</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
         <v>650</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1.27</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>86</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25</v>
       </c>
-      <c r="J12" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K12" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3">
+        <v>412</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="E13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3">
         <v>650</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>10</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>1.27</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>86</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>25</v>
       </c>
-      <c r="J13" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3">
+        <v>413</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>650</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1.3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>160</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>41</v>
       </c>
-      <c r="J14" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3">
+        <v>414</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
         <v>650</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1.3</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>160</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>41</v>
       </c>
-      <c r="J15" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3">
+        <v>415</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="E16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3">
         <v>650</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>20</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>1.3</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>160</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>41</v>
       </c>
-      <c r="J16" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3">
+        <v>416</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>650</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1.3</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>180</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55</v>
       </c>
-      <c r="J17" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3">
+        <v>417</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
         <v>650</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1.3</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>180</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55</v>
       </c>
-      <c r="J18" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K18" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3">
+        <v>418</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="E19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3">
         <v>650</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>1.3</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>300</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>110</v>
       </c>
-      <c r="J19" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3">
+        <v>419</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
-        <v>5</v>
-      </c>
       <c r="G20" s="3">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>1.4</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>55</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25</v>
       </c>
-      <c r="J20" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K20" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3">
+        <v>420</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="F21" s="3">
-        <v>5</v>
-      </c>
       <c r="G21" s="3">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
         <v>1.4</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>55</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25</v>
       </c>
-      <c r="J21" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3">
+        <v>421</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1.4</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>90</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41</v>
       </c>
-      <c r="J22" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3">
+        <v>422</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1.4</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>90</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41</v>
       </c>
-      <c r="J23" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3">
+        <v>423</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1.4</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>90</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41</v>
       </c>
-      <c r="J24" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K24" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3">
+        <v>424</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="E25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
         <v>1200</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G25" s="3">
         <v>10</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>1.4</v>
       </c>
-      <c r="H25" s="3">
+      <c r="I25" s="3">
         <v>90</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J25" s="3">
         <v>41</v>
       </c>
-      <c r="J25" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K25" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3">
+        <v>425</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1.4</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>135</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>62</v>
       </c>
-      <c r="J26" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K26" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3">
+        <v>426</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1.4</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>135</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>62</v>
       </c>
-      <c r="J27" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K27" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3">
+        <v>427</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="E28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3">
         <v>1200</v>
       </c>
-      <c r="F28" s="3">
+      <c r="G28" s="3">
         <v>15</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>1.4</v>
       </c>
-      <c r="H28" s="3">
+      <c r="I28" s="3">
         <v>135</v>
       </c>
-      <c r="I28" s="3">
+      <c r="J28" s="3">
         <v>62</v>
       </c>
-      <c r="J28" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K28" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3">
+        <v>428</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
         <v>1200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>20</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>1.4</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>180</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>80</v>
       </c>
-      <c r="J29" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3">
+        <v>429</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="E30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="3">
         <v>1200</v>
       </c>
-      <c r="F30" s="3">
+      <c r="G30" s="3">
         <v>20</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>1.4</v>
       </c>
-      <c r="H30" s="3">
+      <c r="I30" s="3">
         <v>180</v>
       </c>
-      <c r="I30" s="3">
+      <c r="J30" s="3">
         <v>80</v>
       </c>
-      <c r="J30" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3">
+        <v>430</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="E31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3">
         <v>1200</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <v>20</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>1.4</v>
       </c>
-      <c r="H31" s="3">
+      <c r="I31" s="3">
         <v>180</v>
       </c>
-      <c r="I31" s="3">
+      <c r="J31" s="3">
         <v>82</v>
       </c>
-      <c r="J31" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3">
+        <v>431</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1.4</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>180</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>80</v>
       </c>
-      <c r="J32" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3">
+        <v>432</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1.4</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>240</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>78</v>
       </c>
-      <c r="J33" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K33" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3">
+        <v>433</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E34" s="3">
+      <c r="E34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3">
         <v>1200</v>
       </c>
-      <c r="F34" s="3">
+      <c r="G34" s="3">
         <v>30</v>
       </c>
-      <c r="G34" s="3">
+      <c r="H34" s="3">
         <v>1.4</v>
       </c>
-      <c r="H34" s="3">
+      <c r="I34" s="3">
         <v>270</v>
       </c>
-      <c r="I34" s="3">
+      <c r="J34" s="3">
         <v>78</v>
       </c>
-      <c r="J34" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K34" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3">
+        <v>434</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>40</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1.4</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>109</v>
       </c>
-      <c r="J35" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3">
+        <v>435</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E36" s="3">
+      <c r="E36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="3">
         <v>1200</v>
       </c>
-      <c r="F36" s="3">
+      <c r="G36" s="3">
         <v>40</v>
       </c>
-      <c r="G36" s="3">
+      <c r="H36" s="3">
         <v>1.4</v>
       </c>
-      <c r="H36" s="3">
+      <c r="I36" s="3">
         <v>360</v>
       </c>
-      <c r="I36" s="3">
+      <c r="J36" s="3">
         <v>109</v>
       </c>
-      <c r="J36" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3">
+        <v>436</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="3">
+      <c r="F37" s="3">
         <v>1700</v>
       </c>
-      <c r="F37" s="3">
+      <c r="G37" s="3">
         <v>10</v>
       </c>
-      <c r="G37" s="3">
+      <c r="H37" s="3">
         <v>1.5</v>
-      </c>
-      <c r="H37" s="3">
-        <v>110</v>
       </c>
       <c r="I37" s="3">
         <v>110</v>
       </c>
       <c r="J37" s="3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K37" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3">
+        <v>437</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="3">
+      <c r="F38" s="3">
         <v>1700</v>
       </c>
-      <c r="F38" s="3">
+      <c r="G38" s="3">
         <v>25</v>
       </c>
-      <c r="G38" s="3">
+      <c r="H38" s="3">
         <v>1.6</v>
       </c>
-      <c r="H38" s="3">
+      <c r="I38" s="3">
         <v>120</v>
       </c>
-      <c r="I38" s="3">
+      <c r="J38" s="3">
         <v>82</v>
       </c>
-      <c r="J38" s="3">
+      <c r="K38" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3">
+        <v>438</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="3">
+      <c r="F39" s="3">
         <v>1700</v>
       </c>
-      <c r="F39" s="3">
+      <c r="G39" s="3">
         <v>50</v>
       </c>
-      <c r="G39" s="3">
+      <c r="H39" s="3">
         <v>1.6</v>
       </c>
-      <c r="H39" s="3">
+      <c r="I39" s="3">
         <v>250</v>
       </c>
-      <c r="I39" s="3">
+      <c r="J39" s="3">
         <v>505</v>
       </c>
-      <c r="J39" s="3">
+      <c r="K39" s="3">
         <v>175</v>
       </c>
     </row>
